--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4427977997158401</v>
+        <v>0.442794680589838</v>
       </c>
       <c r="C2">
-        <v>0.6176863218124681</v>
+        <v>0.6162296117104964</v>
       </c>
       <c r="D2">
-        <v>0.701551440642474</v>
+        <v>0.7002043273743609</v>
       </c>
       <c r="E2">
-        <v>0.7524358076969213</v>
+        <v>0.7522860507893896</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4579252394377268</v>
+        <v>0.4579221100507764</v>
       </c>
       <c r="C3">
-        <v>0.6298513683933809</v>
+        <v>0.628504755825571</v>
       </c>
       <c r="D3">
-        <v>0.7078925321183754</v>
+        <v>0.7063599027711679</v>
       </c>
       <c r="E3">
-        <v>0.7564170359425745</v>
+        <v>0.7562245264861476</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.419720720517589</v>
+        <v>0.4197176574654119</v>
       </c>
       <c r="C4">
-        <v>0.6008184859805357</v>
+        <v>0.5997027265756183</v>
       </c>
       <c r="D4">
-        <v>0.6933055670541942</v>
+        <v>0.6919681603173675</v>
       </c>
       <c r="E4">
-        <v>0.7467924631479942</v>
+        <v>0.7465967585015808</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4832906298672929</v>
+        <v>0.4832874750376</v>
       </c>
       <c r="C5">
-        <v>0.6507913071018955</v>
+        <v>0.6478799216700447</v>
       </c>
       <c r="D5">
-        <v>0.7117190287704004</v>
+        <v>0.7097830060621994</v>
       </c>
       <c r="E5">
-        <v>0.763918153379728</v>
+        <v>0.7636218546345843</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4783105745515474</v>
+        <v>0.4783074291455442</v>
       </c>
       <c r="C6">
-        <v>0.6465461535710778</v>
+        <v>0.6436767073653823</v>
       </c>
       <c r="D6">
-        <v>0.709718135770374</v>
+        <v>0.7077923235746036</v>
       </c>
       <c r="E6">
-        <v>0.7625457610805318</v>
+        <v>0.762250841063698</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.4906483264618737</v>
+        <v>0.4906451742252135</v>
       </c>
       <c r="C7">
-        <v>0.6549461698890082</v>
+        <v>0.651985040046865</v>
       </c>
       <c r="D7">
-        <v>0.7201921729891058</v>
+        <v>0.7182202071614885</v>
       </c>
       <c r="E7">
-        <v>0.7644317724559087</v>
+        <v>0.7641379473065246</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4243618638141485</v>
+        <v>0.4243587551396946</v>
       </c>
       <c r="C8">
-        <v>0.5961646260276713</v>
+        <v>0.5996683719996172</v>
       </c>
       <c r="D8">
-        <v>0.6911889526972824</v>
+        <v>0.6940331407047413</v>
       </c>
       <c r="E8">
-        <v>0.7431321011672083</v>
+        <v>0.7435263617765947</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.4849542988768999</v>
+        <v>0.4849511372298663</v>
       </c>
       <c r="C9">
-        <v>0.6497804739386871</v>
+        <v>0.6473501211790124</v>
       </c>
       <c r="D9">
-        <v>0.7174256421780868</v>
+        <v>0.7155647131582599</v>
       </c>
       <c r="E9">
-        <v>0.7627814978018569</v>
+        <v>0.7625033032669952</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.4948320011300388</v>
+        <v>0.4948288880490032</v>
       </c>
       <c r="C10">
-        <v>0.6557084768085584</v>
+        <v>0.6527625053743096</v>
       </c>
       <c r="D10">
-        <v>0.7192211507500265</v>
+        <v>0.7173122770036456</v>
       </c>
       <c r="E10">
-        <v>0.7627957419852761</v>
+        <v>0.7625549981841466</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.4944173734453672</v>
+        <v>0.49457034641241</v>
       </c>
       <c r="C11">
-        <v>0.6560590397357804</v>
+        <v>0.6532446931006516</v>
       </c>
       <c r="D11">
-        <v>0.7198608049094366</v>
+        <v>0.7179885696935229</v>
       </c>
       <c r="E11">
-        <v>0.7634202320927728</v>
+        <v>0.7631940235267909</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4849535997546612</v>
+        <v>0.4850647510340158</v>
       </c>
       <c r="C12">
-        <v>0.6464965173239271</v>
+        <v>0.6435563152521299</v>
       </c>
       <c r="D12">
-        <v>0.7135288818346025</v>
+        <v>0.7115593736496669</v>
       </c>
       <c r="E12">
-        <v>0.7571573853816395</v>
+        <v>0.7568676496393121</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4938201023773014</v>
+        <v>0.4938169932699378</v>
       </c>
       <c r="C13">
-        <v>0.6546031863939528</v>
+        <v>0.6516205864456877</v>
       </c>
       <c r="D13">
-        <v>0.7183637077962255</v>
+        <v>0.7164493622181854</v>
       </c>
       <c r="E13">
-        <v>0.7619929502133752</v>
+        <v>0.7617501679752831</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.442794680589838</v>
+        <v>1.496221785969136</v>
       </c>
       <c r="C2">
-        <v>0.6162296117104964</v>
+        <v>0.9798897355075256</v>
       </c>
       <c r="D2">
-        <v>0.7002043273743609</v>
+        <v>0.5735805508072606</v>
       </c>
       <c r="E2">
-        <v>0.7522860507893896</v>
+        <v>0.404774942393601</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4579221100507764</v>
+        <v>0.8680013569569356</v>
       </c>
       <c r="C3">
-        <v>0.628504755825571</v>
+        <v>0.6453222603462011</v>
       </c>
       <c r="D3">
-        <v>0.7063599027711679</v>
+        <v>0.5966928836418423</v>
       </c>
       <c r="E3">
-        <v>0.7562245264861476</v>
+        <v>0.5757163503065619</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.4197176574654119</v>
+        <v>1.023816545508612</v>
       </c>
       <c r="C4">
-        <v>0.5997027265756183</v>
+        <v>0.7777197464643806</v>
       </c>
       <c r="D4">
-        <v>0.6919681603173675</v>
+        <v>0.5626389064943087</v>
       </c>
       <c r="E4">
-        <v>0.7465967585015808</v>
+        <v>0.4702773687235219</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4832874750376</v>
+        <v>0.120447807246213</v>
       </c>
       <c r="C5">
-        <v>0.6478799216700447</v>
+        <v>0.1624714354652433</v>
       </c>
       <c r="D5">
-        <v>0.7097830060621994</v>
+        <v>0.1768963838637989</v>
       </c>
       <c r="E5">
-        <v>0.7636218546345843</v>
+        <v>0.1914965022458245</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4783074291455442</v>
+        <v>0.5265604954614896</v>
       </c>
       <c r="C6">
-        <v>0.6436767073653823</v>
+        <v>0.5575968904520595</v>
       </c>
       <c r="D6">
-        <v>0.7077923235746036</v>
+        <v>0.6678827176387452</v>
       </c>
       <c r="E6">
-        <v>0.762250841063698</v>
+        <v>0.8695103822413202</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.4906451742252135</v>
+        <v>0.9322258310279056</v>
       </c>
       <c r="C7">
-        <v>0.651985040046865</v>
+        <v>0.6193857880445217</v>
       </c>
       <c r="D7">
-        <v>0.7182202071614885</v>
+        <v>0.6202810880031034</v>
       </c>
       <c r="E7">
-        <v>0.7641379473065246</v>
+        <v>0.6049425416176654</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4243587551396946</v>
+        <v>0.1060574720558666</v>
       </c>
       <c r="C8">
-        <v>0.5996683719996172</v>
+        <v>0.1500536709771286</v>
       </c>
       <c r="D8">
-        <v>0.6940331407047413</v>
+        <v>0.1734555951412092</v>
       </c>
       <c r="E8">
-        <v>0.7435263617765947</v>
+        <v>0.1858251429523649</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.4849511372298663</v>
+        <v>0.9005442016624109</v>
       </c>
       <c r="C9">
-        <v>0.6473501211790124</v>
+        <v>0.7536964012277483</v>
       </c>
       <c r="D9">
-        <v>0.7155647131582599</v>
+        <v>0.6130322523876557</v>
       </c>
       <c r="E9">
-        <v>0.7625033032669952</v>
+        <v>0.5317633921584101</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.4948288880490032</v>
+        <v>0.1244222926597205</v>
       </c>
       <c r="C10">
-        <v>0.6527625053743096</v>
+        <v>0.1622473279254065</v>
       </c>
       <c r="D10">
-        <v>0.7173122770036456</v>
+        <v>0.1803646476858877</v>
       </c>
       <c r="E10">
-        <v>0.7625549981841466</v>
+        <v>0.1895367914561752</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.49457034641241</v>
+        <v>0.1276310571386865</v>
       </c>
       <c r="C11">
-        <v>0.6532446931006516</v>
+        <v>0.158043070911448</v>
       </c>
       <c r="D11">
-        <v>0.7179885696935229</v>
+        <v>0.1737069120226265</v>
       </c>
       <c r="E11">
-        <v>0.7631940235267909</v>
+        <v>0.1969532963940105</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4850647510340158</v>
+        <v>0.4511790537913842</v>
       </c>
       <c r="C12">
-        <v>0.6435563152521299</v>
+        <v>0.5507131034134995</v>
       </c>
       <c r="D12">
-        <v>0.7115593736496669</v>
+        <v>0.7193708241501335</v>
       </c>
       <c r="E12">
-        <v>0.7568676496393121</v>
+        <v>0.9918037638935102</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4938169932699378</v>
+        <v>0.1240873470268048</v>
       </c>
       <c r="C13">
-        <v>0.6516205864456877</v>
+        <v>0.1603989135866308</v>
       </c>
       <c r="D13">
-        <v>0.7164493622181854</v>
+        <v>0.180030865377903</v>
       </c>
       <c r="E13">
-        <v>0.7617501679752831</v>
+        <v>0.1914141447732763</v>
       </c>
     </row>
   </sheetData>
